--- a/Jobs/Tasks/FileProcess/PolicyExcel.xlsx
+++ b/Jobs/Tasks/FileProcess/PolicyExcel.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="48">
   <si>
     <t>OrgId</t>
   </si>
@@ -87,9 +87,6 @@
     <t>ModalBaseRiderPremium</t>
   </si>
   <si>
-    <t>POL-8821</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -145,6 +142,27 @@
   </si>
   <si>
     <t>EFGHI6543Q</t>
+  </si>
+  <si>
+    <t>ProdCode</t>
+  </si>
+  <si>
+    <t>PC001</t>
+  </si>
+  <si>
+    <t>PC002</t>
+  </si>
+  <si>
+    <t>PC003</t>
+  </si>
+  <si>
+    <t>PC004</t>
+  </si>
+  <si>
+    <t>PC005</t>
+  </si>
+  <si>
+    <t>POL-8921</t>
   </si>
 </sst>
 </file>
@@ -423,6 +441,7 @@
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="9" max="9" width="16.08984375" customWidth="1"/>
+    <col min="22" max="22" width="22.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="13" x14ac:dyDescent="0.3">
@@ -492,7 +511,9 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2"/>
+      <c r="W1" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
@@ -501,10 +522,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="D2" s="4">
         <v>45292</v>
@@ -519,10 +540,10 @@
         <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J2" s="3">
         <v>108</v>
@@ -534,10 +555,10 @@
         <v>1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O2" s="4">
         <v>33008</v>
@@ -562,6 +583,9 @@
       </c>
       <c r="V2" s="3">
         <v>150</v>
+      </c>
+      <c r="W2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -569,7 +593,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4">
@@ -585,10 +609,10 @@
         <v>15</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="J3" s="3">
         <v>36</v>
@@ -600,10 +624,10 @@
         <v>2</v>
       </c>
       <c r="M3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="O3" s="4">
         <v>31340</v>
@@ -628,6 +652,9 @@
       </c>
       <c r="V3" s="3">
         <v>300.75</v>
+      </c>
+      <c r="W3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -635,7 +662,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="4">
@@ -651,10 +678,10 @@
         <v>15</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J4" s="3">
         <v>30</v>
@@ -666,10 +693,10 @@
         <v>1</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O4" s="4">
         <v>35038</v>
@@ -694,6 +721,9 @@
       </c>
       <c r="V4" s="3">
         <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -701,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="4">
@@ -717,10 +747,10 @@
         <v>20</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="J5" s="3">
         <v>41</v>
@@ -732,10 +762,10 @@
         <v>3</v>
       </c>
       <c r="M5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="O5" s="4">
         <v>36526</v>
@@ -760,6 +790,9 @@
       </c>
       <c r="V5" s="3">
         <v>450.5</v>
+      </c>
+      <c r="W5" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -767,7 +800,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4">
@@ -783,10 +816,10 @@
         <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="3">
         <v>7</v>
@@ -798,10 +831,10 @@
         <v>1</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O6" s="4">
         <v>25805</v>
@@ -826,6 +859,9 @@
       </c>
       <c r="V6" s="3">
         <v>100</v>
+      </c>
+      <c r="W6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
